--- a/test/db.xlsx
+++ b/test/db.xlsx
@@ -64,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,39 +397,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
         <v>created</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>priority</v>
       </c>
-      <c r="C1" t="str">
-        <v>description</v>
-      </c>
       <c r="D1" t="str">
+        <v>desc</v>
+      </c>
+      <c r="E1" t="str">
         <v>due</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
-        <v>45189.35763888889</v>
-      </c>
-      <c r="B2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2023-10-01T06:57:17.048Z</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>aaa</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="C2" t="str">
-        <v>aaa</v>
-      </c>
-      <c r="D2" s="1">
-        <v>45189.37777777778</v>
+      <c r="B3" t="str">
+        <v>2023-10-01T06:58:17.048Z</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>bbb</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>